--- a/output/pdf_financials_xlsx/SFR.xlsx
+++ b/output/pdf_financials_xlsx/SFR.xlsx
@@ -5951,40 +5951,40 @@
         <v>1.766765</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.514343</v>
+        <v>2.58578</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.709102</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.911397</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.095848</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>13.323442</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>13.468909</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>13.533441</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.662853</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>10.98215</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.937302</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.054356</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.007572</v>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
@@ -14643,7 +14643,11 @@
           <t>Share-based payment reserve (Note 11) 8,124,251</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -16983,7 +16987,11 @@
           <t>Share-based payment reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -17834,7 +17842,11 @@
           <t>Warrants reserve (Notes 2.q and 11)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -17933,7 +17945,11 @@
           <t>Share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -18434,7 +18450,11 @@
           <t>Warrants reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -19113,7 +19133,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -19212,7 +19236,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -19881,7 +19909,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -19980,7 +20012,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -20166,7 +20202,11 @@
           <t>Warrants Reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -20362,7 +20402,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SFR.xlsx
+++ b/output/pdf_financials_xlsx/SFR.xlsx
@@ -1035,37 +1035,37 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.149218</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.24645</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.095279</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.031379</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.092144</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.008259000000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.006001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.00049</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.013531</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>5.4e-05</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1979,37 +1979,37 @@
         <v>-2.557948</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.98763</v>
+        <v>-12.136848</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-15.085247</v>
+        <v>-15.331697</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.788468</v>
+        <v>-9.883747</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.524288</v>
+        <v>-5.555667</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-10.847879</v>
+        <v>-10.940023</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.704896</v>
+        <v>-4.713155</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-6.454349</v>
+        <v>-6.46035</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-9.979499000000001</v>
+        <v>-9.979989</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-14.194658</v>
+        <v>-14.208189</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-10.863128</v>
+        <v>-10.863318</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.982148</v>
+        <v>-10.982202</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-18.970085</v>
@@ -2095,37 +2095,37 @@
         <v>-2.557948</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.940746</v>
+        <v>-12.089964</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-15.070407</v>
+        <v>-15.316857</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.774721</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.51201</v>
+        <v>-5.543389</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-10.839382</v>
+        <v>-10.931526</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.701117</v>
+        <v>-4.709376</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-6.450905</v>
+        <v>-6.456906</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-9.936631999999999</v>
+        <v>-9.937122</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-14.060796</v>
+        <v>-14.074327</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-10.622165</v>
+        <v>-10.622355</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.706809</v>
+        <v>-10.706863</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-18.767019</v>
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.740781</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.09848</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.740781</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.09848</v>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.854385</v>
+        <v>0.113604</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.199814</v>
@@ -12811,7 +12811,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -38889,7 +38889,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -42088,7 +42088,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -42173,7 +42173,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">

--- a/output/pdf_financials_xlsx/SFR.xlsx
+++ b/output/pdf_financials_xlsx/SFR.xlsx
@@ -7095,10 +7095,10 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.00195</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.002089</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -31739,7 +31739,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -39653,7 +39657,11 @@
           <t>Depreciation of property and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -39752,7 +39760,11 @@
           <t>Depreciation of right of use asset</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SFR.xlsx
+++ b/output/pdf_financials_xlsx/SFR.xlsx
@@ -745,7 +745,7 @@
         <v>0.653051</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.502533</v>
+        <v>0.525477</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.780099</v>
@@ -919,7 +919,7 @@
         <v>2.423778</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.801585</v>
+        <v>0.824529</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.08245</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2.625766</v>
+        <v>-2.625766</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1334,7 +1334,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.49595</v>
+        <v>-0.49595</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0.98095</v>
@@ -1352,7 +1352,7 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.0042</v>
+        <v>-0.0042</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -4235,25 +4235,25 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.014226</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.234897</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.504744</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.113149</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.204179</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.792121</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.23159</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         </is>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.413872</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.601371</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.6409</v>
       </c>
     </row>
     <row r="65">
@@ -4415,54 +4415,52 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.232843</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.488712</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.257857</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.209075</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.200533</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.338723</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.389788</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.213676</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.262299</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.320211</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.5135189999999999</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.222574</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>0.634835</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.593472</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.11306</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>1.605444</v>
       </c>
     </row>
     <row r="68">
@@ -7013,28 +7011,28 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.039049</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.040468</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.018994</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017626</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.020181</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001651</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002303</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001651</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>-0.002492</v>
@@ -8381,28 +8379,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.039049</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.040468</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.018994</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017626</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020181</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001651</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002303</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001651</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>-0.002492</v>
@@ -8439,28 +8437,28 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.46365</v>
+        <v>-1.502699</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.493007</v>
+        <v>-1.533475</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-8.389172</v>
+        <v>-8.408166</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-14.21536</v>
+        <v>-14.232986</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-7.770402</v>
+        <v>-7.790583</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-4.719858</v>
+        <v>-4.721509</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-10.04396</v>
+        <v>-10.046263</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-5.138646</v>
+        <v>-5.140297</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-6.433231</v>
@@ -29538,7 +29536,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -31537,7 +31539,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -32729,7 +32735,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -33517,7 +33527,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -34097,7 +34111,11 @@
           <t>Purchase of equipment, net</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E260" s="5" t="n">
         <v>-0.039049</v>
       </c>
@@ -35792,7 +35810,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -36206,7 +36228,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E281" s="5" t="n">
         <v>-2.625766</v>
       </c>
@@ -36923,7 +36949,11 @@
           <t>Proceeds from share issuances, net</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E288" s="5" t="n">
         <v>5.0651</v>
       </c>
@@ -42476,7 +42506,11 @@
           <t>Income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -43749,7 +43783,11 @@
           <t>Income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -45440,7 +45478,11 @@
           <t>Income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -46432,7 +46474,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -47832,7 +47878,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -49961,7 +50011,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 11)</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>2.625766</v>
       </c>
